--- a/src/test/resources/users2.xlsx
+++ b/src/test/resources/users2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="14">
   <si>
     <t>UserType</t>
   </si>
@@ -48,7 +48,16 @@
     <t>Mi@12345678</t>
   </si>
   <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>saved</t>
+  </si>
+  <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
@@ -388,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="12.5546875"/>
@@ -428,8 +437,11 @@
       <c r="D2" s="0">
         <v>1</v>
       </c>
+      <c r="E2" t="s" s="0">
+        <v>10</v>
+      </c>
       <c r="F2" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -445,8 +457,11 @@
       <c r="D3" s="0">
         <v>1</v>
       </c>
+      <c r="E3" t="s" s="0">
+        <v>11</v>
+      </c>
       <c r="F3" t="s" s="0">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -462,8 +477,48 @@
       <c r="D4" s="0">
         <v>4</v>
       </c>
+      <c r="E4" t="s" s="0">
+        <v>11</v>
+      </c>
       <c r="F4" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D6" s="0">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
